--- a/test/data/Bulk_Upload_Bookings.xlsx
+++ b/test/data/Bulk_Upload_Bookings.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohammed.ubeduddin\Documents\LanguageLoop\Repo\ll-ui-test-automation\premaster\ll-ui-test-automation\test\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibase1-my.sharepoint.com/personal/keerthi_kodakandla_qualitestgroup_com/Documents/LL/Automation_LL/Premaster_FinalCopy/ll-ui-test-automation/test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_A168384FC2E2221AB99B176D47CADDEA62BE7D0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EF42953-6247-4AC0-B782-487476C74BBC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21540" windowHeight="9630"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulk_Upload_Template" sheetId="1" r:id="rId1"/>
@@ -277,8 +278,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="21" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,27 +799,26 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,13 +845,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="33" borderId="5" xfId="10" applyFill="1" applyAlignment="1">
@@ -888,7 +882,7 @@
     </xf>
     <xf numFmtId="14" fontId="10" fillId="33" borderId="5" xfId="10" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="10" fillId="33" borderId="5" xfId="10" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="20" fillId="33" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -902,10 +896,8 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="5" xfId="10" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="5" xfId="10" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="19" fillId="33" borderId="5" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="19" fillId="33" borderId="5" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="20" fillId="33" borderId="5" xfId="10" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1269,694 +1261,693 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7265625" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" customWidth="1"/>
-    <col min="8" max="8" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.7265625" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" style="48" customWidth="1"/>
-    <col min="12" max="12" width="23.54296875" customWidth="1"/>
-    <col min="13" max="13" width="22.81640625" customWidth="1"/>
-    <col min="14" max="14" width="23.1796875" customWidth="1"/>
-    <col min="15" max="15" width="29.26953125" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" customWidth="1"/>
-    <col min="17" max="17" width="27.453125" customWidth="1"/>
-    <col min="18" max="18" width="12.453125" customWidth="1"/>
-    <col min="19" max="19" width="11.1796875" customWidth="1"/>
-    <col min="20" max="20" width="14.26953125" customWidth="1"/>
-    <col min="21" max="21" width="28.81640625" customWidth="1"/>
-    <col min="22" max="22" width="27.26953125" customWidth="1"/>
+    <col min="10" max="10" width="32.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" style="43" customWidth="1"/>
+    <col min="12" max="12" width="23.5703125" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" customWidth="1"/>
+    <col min="15" max="15" width="29.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.140625" customWidth="1"/>
+    <col min="17" max="17" width="27.42578125" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" customWidth="1"/>
+    <col min="21" max="21" width="28.85546875" customWidth="1"/>
+    <col min="22" max="22" width="27.28515625" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="10.26953125" customWidth="1"/>
-    <col min="25" max="25" width="6.81640625" customWidth="1"/>
-    <col min="26" max="26" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="31.81640625" customWidth="1"/>
-    <col min="28" max="28" width="31.81640625" style="4" customWidth="1"/>
-    <col min="29" max="29" width="32.26953125" customWidth="1"/>
-    <col min="30" max="30" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.28515625" customWidth="1"/>
+    <col min="25" max="25" width="6.85546875" customWidth="1"/>
+    <col min="26" max="26" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="31.85546875" customWidth="1"/>
+    <col min="29" max="29" width="32.28515625" customWidth="1"/>
+    <col min="30" max="30" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="60">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="P1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="Q1" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="T1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="24" t="s">
+      <c r="U1" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="24" t="s">
+      <c r="V1" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="24" t="s">
+      <c r="W1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="24" t="s">
+      <c r="X1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="Y1" s="24" t="s">
+      <c r="Y1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="24" t="s">
+      <c r="AB1" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="AC1" s="21" t="s">
+      <c r="AC1" s="18" t="s">
         <v>48</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:30">
+      <c r="A2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="36">
-        <v>45566</v>
-      </c>
-      <c r="C2" s="37">
+      <c r="B2" s="33">
+        <v>45931</v>
+      </c>
+      <c r="C2" s="34">
         <v>0.375</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="35">
         <v>90</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39" t="s">
+      <c r="F2" s="36"/>
+      <c r="G2" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="J2" s="35" t="s">
+      <c r="H2" s="37"/>
+      <c r="J2" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="46" t="s">
+      <c r="K2" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40"/>
-      <c r="N2" s="39" t="s">
+      <c r="M2" s="37"/>
+      <c r="N2" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39" t="s">
+      <c r="O2" s="36"/>
+      <c r="P2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="42" t="s">
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="38" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:30">
+      <c r="A3" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="36">
-        <v>45601</v>
-      </c>
-      <c r="C3" s="37">
+      <c r="B3" s="33">
+        <v>45966</v>
+      </c>
+      <c r="C3" s="34">
         <v>0.4375</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="35">
         <v>120</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39" t="s">
+      <c r="F3" s="36"/>
+      <c r="G3" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="39" t="s">
+      <c r="H3" s="37"/>
+      <c r="I3" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="K3" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="L3" s="39"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="39" t="s">
+      <c r="L3" s="36"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39" t="s">
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="S3" s="39" t="s">
+      <c r="S3" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="T3" s="39"/>
-      <c r="U3" s="38"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39" t="s">
+      <c r="T3" s="36"/>
+      <c r="U3" s="35"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="42" t="s">
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="AD3" s="42" t="s">
+      <c r="AD3" s="38" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:30">
+      <c r="A4" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="36">
-        <v>45602</v>
-      </c>
-      <c r="C4" s="37">
+      <c r="B4" s="33">
+        <v>45967</v>
+      </c>
+      <c r="C4" s="34">
         <v>0.46875</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="35">
         <v>60</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39" t="s">
+      <c r="F4" s="36"/>
+      <c r="G4" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="39" t="s">
+      <c r="H4" s="37"/>
+      <c r="I4" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="46" t="s">
+      <c r="J4" s="36"/>
+      <c r="K4" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="44" t="s">
+      <c r="L4" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="40"/>
-      <c r="N4" s="39" t="s">
+      <c r="M4" s="37"/>
+      <c r="N4" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="U4" s="38" t="s">
+      <c r="U4" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39" t="s">
+      <c r="V4" s="36"/>
+      <c r="W4" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="X4" s="39" t="s">
+      <c r="X4" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="Y4" s="39" t="s">
+      <c r="Y4" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="Z4" s="39"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="42" t="s">
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" s="42" t="s">
+      <c r="AD4" s="38" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="31"/>
-      <c r="Z5" s="31"/>
-      <c r="AA5" s="31"/>
-      <c r="AB5" s="31"/>
-      <c r="AC5" s="22"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A7" s="22"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A8" s="22"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A12" s="22"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A13" s="22"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A14" s="22"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A15" s="22"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="22"/>
+    <row r="5" spans="1:30">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="19"/>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="A6" s="19"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+    </row>
+    <row r="7" spans="1:30">
+      <c r="A7" s="19"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+    </row>
+    <row r="8" spans="1:30">
+      <c r="A8" s="19"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="19"/>
+    </row>
+    <row r="9" spans="1:30">
+      <c r="A9" s="19"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+    </row>
+    <row r="10" spans="1:30">
+      <c r="A10" s="19"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+    </row>
+    <row r="11" spans="1:30">
+      <c r="A11" s="19"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+    </row>
+    <row r="12" spans="1:30">
+      <c r="A12" s="19"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+    </row>
+    <row r="13" spans="1:30">
+      <c r="A13" s="19"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+    </row>
+    <row r="14" spans="1:30">
+      <c r="A14" s="19"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
+      <c r="AC14" s="19"/>
+    </row>
+    <row r="15" spans="1:30">
+      <c r="A15" s="19"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+    </row>
+    <row r="16" spans="1:30">
+      <c r="A16" s="19"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1"/>
-    <hyperlink ref="L2" r:id="rId2"/>
+    <hyperlink ref="L4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -1967,488 +1958,483 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.453125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="3" style="4" customWidth="1"/>
-    <col min="7" max="7" width="56.1796875" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="4"/>
+    <col min="1" max="1" width="24.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="3" customWidth="1"/>
+    <col min="7" max="7" width="56.140625" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="G1" s="17"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>50</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>10</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>43476</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:7">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>11</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="14">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>3</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>100</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>100</v>
       </c>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>100</v>
       </c>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>10</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>100</v>
       </c>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <v>250</v>
       </c>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>10</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="20"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>100</v>
       </c>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <v>10</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>150</v>
       </c>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <v>500</v>
       </c>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <v>3</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <v>500</v>
       </c>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19" spans="1:5" ht="30">
+      <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <v>6</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:5" ht="30">
+      <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <v>9</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:5" ht="30">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <v>250</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <v>200</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="12" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <v>200</v>
       </c>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="E23" s="12"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <v>50</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <v>4</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <v>3075</v>
       </c>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="30">
+      <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <v>3</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <v>150</v>
       </c>
-      <c r="E27" s="13"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="12">
         <v>150</v>
       </c>
-      <c r="E28" s="13"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="20">
         <v>2000</v>
       </c>
     </row>

--- a/test/data/Bulk_Upload_Bookings.xlsx
+++ b/test/data/Bulk_Upload_Bookings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibase1-my.sharepoint.com/personal/keerthi_kodakandla_qualitestgroup_com/Documents/LL/Automation_LL/Premaster_FinalCopy/ll-ui-test-automation/test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_A168384FC2E2221AB99B176D47CADDEA62BE7D0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EF42953-6247-4AC0-B782-487476C74BBC}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_A168384FC2E2221AB99B176D47CADDEA62BE7D0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F9700E-E34B-45D4-B004-D385F6E17532}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1393,7 +1393,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="33">
-        <v>45931</v>
+        <v>47027</v>
       </c>
       <c r="C2" s="34">
         <v>0.375</v>
@@ -1450,7 +1450,7 @@
         <v>56</v>
       </c>
       <c r="B3" s="33">
-        <v>45966</v>
+        <v>47062</v>
       </c>
       <c r="C3" s="34">
         <v>0.4375</v>
@@ -1511,7 +1511,7 @@
         <v>62</v>
       </c>
       <c r="B4" s="33">
-        <v>45967</v>
+        <v>47063</v>
       </c>
       <c r="C4" s="34">
         <v>0.46875</v>
